--- a/data/quotas/quota_onnuri_서울_풍납시장_온누리쿼터_연락처확인_1791810958944.xlsx
+++ b/data/quotas/quota_onnuri_서울_풍납시장_온누리쿼터_연락처확인_1791810958944.xlsx
@@ -397,18 +397,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.43359375" customWidth="1"/>
     <col min="4" max="4" width="19.234375" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="44.83203125" customWidth="1"/>
-    <col min="9" max="9" width="59.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="44.83203125" customWidth="1"/>
+    <col min="11" max="11" width="45.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -428,18 +430,24 @@
         <v>대표자명</v>
       </c>
       <c r="F1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="G1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="H1" t="str">
         <v>연락처</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>개업연월</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>취급품목</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>주소</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>가맹상태</v>
       </c>
     </row>
@@ -460,22 +468,28 @@
         <v/>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>02-2222-2222</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>2020.10.06</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>수산물 (신선)</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>서울특별시 송파구 바람드리길 37-1 (풍납동)</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>정상가맹</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -495,20 +509,25 @@
         <v/>
       </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>2012.03.13</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>기타소매업 (두발 미용업)</v>
       </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">서울특별시 송파구 바람드리길 27-1 (풍납동)
-주소정보 갱신</v>
-      </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
+        <v>서울특별시 송파구 바람드리길 27-1 (풍납동)</v>
+      </c>
+      <c r="L3" t="str">
         <v>정상가맹</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -525,23 +544,28 @@
         <v/>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>02-111-1113</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>2023.10.06</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>기타소매업 (피부 미용업)</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
-        <v xml:space="preserve">서울특별시 송파구 풍성로25길 37 (풍납동)
-주소정보 갱신</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
+        <v>서울특별시 송파구 풍성로25길 37 (풍납동)</v>
+      </c>
+      <c r="L4" t="str">
         <v>정상가맹</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -561,20 +585,25 @@
         <v/>
       </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>2025.06.11</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <v>농산물 (곡물)</v>
       </c>
-      <c r="I5" t="str" xml:space="preserve">
-        <v xml:space="preserve">서울특별시 송파구 바람드리길 42 (풍납동)
-주소정보 갱신</v>
-      </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
+        <v>서울특별시 송파구 바람드리길 42 (풍납동)</v>
+      </c>
+      <c r="L5" t="str">
         <v>정상가맹</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -591,25 +620,30 @@
         <v>김영주</v>
       </c>
       <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>02-1111-1111</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>2022.03.14</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <v>수산물 (음ㆍ식료품 및 담배 도매업 외 1개)</v>
       </c>
-      <c r="I6" t="str" xml:space="preserve">
-        <v xml:space="preserve">서울특별시 송파구 바람드리길 44 (풍납동)
-주소정보 갱신</v>
-      </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
+        <v>서울특별시 송파구 바람드리길 44 (풍납동)</v>
+      </c>
+      <c r="L6" t="str">
         <v>정상가맹</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>